--- a/database/template-import-export/templates/template-hortikultura.xlsx
+++ b/database/template-import-export/templates/template-hortikultura.xlsx
@@ -30,7 +30,7 @@
     <t>Luas &amp; produksi hortikultura (sayuran/buah) per kecamatan dan agregat kabupaten.</t>
   </si>
   <si>
-    <t>Dibuat otomatis: 22/9/2026, 14.21.29</t>
+    <t>Dibuat otomatis: 29/9/2026, 15.29.39</t>
   </si>
   <si>
     <t>CARA PAKAI</t>
